--- a/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
+++ b/InputData/web-app/OCCF/Output Currency Conversion Factors.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-hongkong\InputData\web-app\OCCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\web-app\OCCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E145C7-DA32-48E1-AEFA-9C38A9EDE413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -17,7 +18,7 @@
     <sheet name="OCCF-DpMOCU" sheetId="4" r:id="rId3"/>
     <sheet name="OCCF-DpSOCU" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -25,6 +26,7 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Source:</t>
   </si>
@@ -82,27 +84,12 @@
     <t>OCCF Dollars per Small Output Currency Unit</t>
   </si>
   <si>
-    <t>billion 2018 dollars</t>
-  </si>
-  <si>
-    <t>2018 dollars</t>
-  </si>
-  <si>
     <t>See cpi.xlsx</t>
   </si>
   <si>
-    <t>which in this case is "2012 dollars per 2018 dollar."</t>
-  </si>
-  <si>
-    <t>2012 dollars are worth more than 2018 dollars, so we need a</t>
-  </si>
-  <si>
     <t>value less than 1 in this variable.</t>
   </si>
   <si>
-    <t>2018 dollars per 2012 dollar</t>
-  </si>
-  <si>
     <t>This is why we multiply, not divide, by the conversion</t>
   </si>
   <si>
@@ -112,25 +99,34 @@
     <t>Medium Output Currency Unit</t>
   </si>
   <si>
-    <t>million 2018 dollars</t>
-  </si>
-  <si>
     <t>OCCF Dollars per Medium Output Currency Unit</t>
   </si>
   <si>
     <t>Recall, this variable is "dollars per large/medium/small currency output unit"</t>
   </si>
   <si>
-    <t>this number was used</t>
-  </si>
-  <si>
-    <t>HKD converted to USD</t>
+    <t>2019 dollars per 2012 dollar</t>
+  </si>
+  <si>
+    <t>2020 dollars</t>
+  </si>
+  <si>
+    <t>million 2020 dollars</t>
+  </si>
+  <si>
+    <t>billion 2020 dollars</t>
+  </si>
+  <si>
+    <t>which in this case is "2012 dollars per 2020 dollar."</t>
+  </si>
+  <si>
+    <t>2012 dollars are worth more than 2020 dollars, so we need a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -174,10 +170,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -278,6 +275,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -313,6 +327,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -488,8 +519,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
@@ -502,7 +533,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -515,7 +546,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -559,91 +590,74 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="6"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="5"/>
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="6"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="6"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>0.9143273584567535</v>
+        <v>0.88711067149387013</v>
       </c>
       <c r="B26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>0.12773839177364757</v>
-      </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <f>A26*A35</f>
-        <v>0.11679470632391308</v>
-      </c>
-      <c r="B36" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +667,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -664,7 +678,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -672,9 +686,9 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7">
-        <f>10^9*About!$A$36</f>
-        <v>116794706.32391308</v>
+      <c r="B2" s="3">
+        <f>10^9*About!$A$26</f>
+        <v>887110671.49387014</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +697,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -694,7 +708,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -702,9 +716,9 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7">
-        <f>10^6*About!$A$36</f>
-        <v>116794.70632391308</v>
+      <c r="B2" s="8">
+        <f>10^6*About!$A$26</f>
+        <v>887110.67149387009</v>
       </c>
     </row>
   </sheetData>
@@ -713,7 +727,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
@@ -724,7 +738,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -732,9 +746,9 @@
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6">
-        <f>1*About!A36</f>
-        <v>0.11679470632391308</v>
+      <c r="B2" s="7">
+        <f>1*About!A26</f>
+        <v>0.88711067149387013</v>
       </c>
     </row>
   </sheetData>
@@ -743,49 +757,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -793,24 +790,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -829,70 +887,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -994,40 +1005,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8916BED6-C418-4D2C-92B1-9B25D4D2165C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89B9B33C-839B-4CB2-9A59-066B2B4708FD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1E47CE-7FF8-41C0-9A62-3DDD9BF31744}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF2806A1-6745-49C6-B2ED-E2AD30734EC2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20B02BC9-50FF-4AB7-86FB-B323EF55E1D9}"/>
 </file>